--- a/docs/07_haip-diff-matrix.xlsx
+++ b/docs/07_haip-diff-matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="HAIP差分一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HAIP差分一覧'!$A$4:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HAIP差分一覧'!$A$4:$H$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,11 +66,21 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +115,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5EF"/>
       </patternFill>
     </fill>
     <fill>
@@ -144,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -174,22 +189,31 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -560,35 +584,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OID4VC HAIP と素の OID4VCI / OID4VP の MUST・任意 差分一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+          <t>OID4VC HAIP と素の OID4VCI / OID4VP の MUST・任意 差分一覧(サンプル・参照リンク付き)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出典: HAIP draft-04(2025-09-19)/ draft-06(2025-11-20)、OID4VCI 1.0-final(2025-09-16)、OID4VP 1.0-final(2025-07-10)。「対象外」= その仕様のスコープ外(発行/提示の別)。draft-06→Final(2025-12)間の差分は未検証。実装判断は各仕様の Final 本文を確認のこと。</t>
+          <t>出典: HAIP draft-04(2025-09-19)/ draft-06(2025-11-20)、OID4VCI 1.0-final(2025-09-16)、OID4VP 1.0-final(2025-07-10)。「対象外」= その仕様のスコープ外。参照リンクのアンカーは xml2rfc標準命名(#name-…)の best-effort。draft-06→Final差分は未検証。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>凡例:  必須 = MUST/REQUIRED   任意 = MAY/OPTIONAL   推奨 = RECOMMENDED/SHOULD   条件付き = 条件により必須   対象外 = 仕様スコープ外   規定なし = 本文で規定せずプロファイルに委譲</t>
+          <t>凡例:  必須=MUST/REQUIRED   任意=MAY/OPTIONAL   推奨=RECOMMENDED/SHOULD   条件付き=条件により必須   対象外=仕様スコープ外   規定なし=本文で規定せずプロファイル委譲</t>
         </is>
       </c>
     </row>
@@ -615,12 +641,22 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>サンプル / 例</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>必須である理由 / 補足</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>参照(仕様・セクション)</t>
         </is>
       </c>
     </row>
@@ -635,8 +671,10 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="76" customHeight="1">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="57" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>認可コードフロー(authorization_code)</t>
@@ -659,22 +697,32 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>VC 発行のためのグラントタイプ。HAIP は authorization_code フローのサポートを必須化。</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>フローを1つに固定することで、発行者とウォレットの実装分岐を減らし相互接続を保証するため。素の OID4VCI では複数の OAuth グラントから選択可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+          <t>grant_type=authorization_code&amp;code=SplxlO...&amp;code_verifier=dBjftJ...</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>VC発行のためのグラントタイプ。HAIP は authorization_code フローを必須化。</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>フローを1つに固定し実装分岐を減らすため。素の VCI は複数の OAuth グラントから選択可。</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Credential Issuance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="87" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>事前認可コードフロー(pre-authorized_code)</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -689,21 +737,31 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>事前に本人確認済みのユーザー向けの簡易発行フロー。</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>HAIP でも MUST ではない(authorization_code のみ必須)。利便性のため任意で併用可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>grant_type=urn:ietf:params:oauth:grant-type:pre-authorized_code&amp;pre-authorized_code=Splx...&amp;tx_code=1234</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>事前本人確認済みユーザー向けの簡易発行フロー。</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>HAIP でも MUST ではない(authorization_code のみ必須)。利便性のため任意併用可。</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>PAR(Pushed Authorization Requests / RFC9126)</t>
+          <t>PAR(RFC9126)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -723,17 +781,27 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>認可リクエストを事前にサーバへ登録し、ブラウザ経由での改ざん・肥大化を防ぐ。</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>HAIP は FAPI2 Security Profile 準拠の一部として必須化。素の VCI では RECOMMENDED どまり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+          <t>POST /par  →  { "request_uri": "urn:ietf:params:oauth:request_uri:6esc_11...", "expires_in": 60 }</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>認可リクエストを事前登録し改ざん・肥大化を防ぐ。</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>HAIP は FAPI2 準拠の一部として必須化。素の VCI では RECOMMENDED。</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>OID4VCI §Authorization Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="57" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>PKCE(S256 / RFC7636)</t>
         </is>
@@ -753,18 +821,28 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>認可コード横取り(interception)攻撃を防ぐコードチャレンジ。</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>HAIP は FAPI2 準拠として S256 を必須化。素の VCI では RECOMMENDED。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="76" customHeight="1">
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>code_challenge=E9Melhoa2Ow...&amp;code_challenge_method=S256</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>認可コード横取り攻撃を防ぐコードチャレンジ。</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>HAIP は FAPI2 準拠として S256 必須。素の VCI では RECOMMENDED。</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Authorization Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="87" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>認可レスポンスへの iss 付与(RFC9207)</t>
@@ -787,19 +865,29 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>認可レスポンスに認可サーバーの識別子(iss)を含め、応答の出所を検証可能にする。</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>HAIP draft-06 で FAPI2 準拠要件の一部として追加。複数認可サーバー利用時のミックスアップ攻撃対策。draft-04 には未記載。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>DPoP(送信者制約トークン / RFC9449)</t>
+          <t>HTTP/1.1 302 Found  Location: https://wallet.example.org/cb?code=Splx...&amp;iss=https%3A%2F%2Fissuer.example.com</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>認可レスポンスに認可サーバー識別子を含め出所を検証可能に。</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>HAIP draft-06 で FAPI2 準拠の一部として追加。ミックスアップ攻撃対策。draft-04 には未記載。</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Credential Issuance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="57" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>DPoP(RFC9449)</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -817,18 +905,28 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>アクセストークンをウォレットの鍵に紐づけ、盗難トークンの悪用を防ぐ。</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>HAIP は MUST。素の VCI では DPoP nonce を MAY 提供とする程度で任意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>DPoP: eyJ0eXAiOiJkcG9wK2p3dCIsImFsZyI6IkVTMjU2IiwiandrIjp7Li4ufX0...</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>アクセストークンをウォレットの鍵に紐づけ盗難悪用を防ぐ。</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>HAIP は MUST。素の VCI では DPoP nonce を MAY 提供する程度で任意。</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Token Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="57" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Wallet Attestation(クライアント認証)</t>
@@ -851,17 +949,27 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>ウォレットが「正規実装であること」を認可サーバーに証明する仕組み。x5c で検証鍵を提示。</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>なりすましクライアント排除のため HAIP で必須化。素の VCI ではクライアント認証方式はクライアント種別依存で任意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+          <t>OAuth-Client-Attestation: eyJ...  /  OAuth-Client-Attestation-PoP: eyJ...</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>ウォレットが正規実装であることを認可サーバーに証明。</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>なりすまし排除のため HAIP で必須化。素の VCI は認証方式がクライアント種別依存で任意。</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §Wallet Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Key Attestation(鍵の保管環境の証明)</t>
         </is>
@@ -881,29 +989,39 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>proof の鍵がセキュアエレメント等で生成・保管されていることを証明。</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>HAIP draft-04 で新規に必須化。素の VCI では proof が鍵証明か所有証明かを選べる任意仕様。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>{ "typ": "key-attestation+jwt", "attested_keys": [ {"kty":"EC","crv":"P-256",...} ] }</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>proof の鍵がセキュアエレメント等で保管されることを証明。</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>HAIP draft-04 で新規必須化。素の VCI は鍵証明/所有証明を選べる任意仕様。</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Key Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="57" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Nonce Endpoint</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -915,17 +1033,27 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>proof のリプレイ防止用チャレンジ(c_nonce)を払い出す専用エンドポイント。</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>両者とも「proof に c_nonce を要求する場合は MUST」。HAIP は暗号バインディングを前提とするため実質必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="92" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+          <t>POST /nonce  →  { "c_nonce": "wKI4LT...oi8" }</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>proof のリプレイ防止用チャレンジ(c_nonce)を払い出す。</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>両者とも「proof に c_nonce を要求するなら MUST」。HAIP は暗号バインディング前提のため実質必須。</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>OID4VCI §Nonce Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="57" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>proof_type(jwt / attestation)</t>
         </is>
@@ -935,7 +1063,7 @@
           <t>必須(両方)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -945,18 +1073,28 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>{ "proofs": { "jwt": ["eyJ0eXAiOiJvcGVuaWQ0dmNpLXByb29mK2p3dCI..."] } }</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>発行時に鍵所有/鍵証明を示す proof の型。</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>HAIP は jwt(key_attestation併用)と attestation の両サポートを必須化。素の VCI は proof_types_supported を示すなら proofs 必須という条件付き。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="76" customHeight="1">
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>HAIP は jwt と attestation の両サポート必須。素の VCI は条件付き。</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>scope によるクレデンシャル種別識別</t>
@@ -979,12 +1117,22 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>どの種別のクレデンシャルを要求するかを scope 値で伝える。</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>HAIP は authorization_code フローで scope 必須。素の VCI では authorization_details との二者択一で任意。</t>
+          <t>GET /authorize?...&amp;scope=employee_credential</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>どの種別のクレデンシャルを要求するかを scope で伝える。</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>HAIP は authorization_code フローで scope 必須。素の VCI は authorization_details との二択で任意。</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>OID4VCI §Authorization Endpoint</t>
         </is>
       </c>
     </row>
@@ -999,8 +1147,10 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="46" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>response_type = vp_token</t>
@@ -1016,26 +1166,36 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
+          <t>response_type=vp_token</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
           <t>VP(提示)を要求・返却するためのレスポンスタイプ。</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>素の VP でも vp_token 応答時は MUST。HAIP も vp_token を必須と明記。</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="108" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>response_mode = direct_post.jwt(リダイレクト方式)</t>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>OID4VP §Response Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="57" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>response_mode = direct_post.jwt(リダイレクト)</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1053,18 +1213,28 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>提示レスポンスを Verifier サーバへ直接 POST し、かつ JWE 暗号化する応答モード。</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>素の VP は fragment / direct_post / direct_post.jwt / dc_api.jwt から選択可。HAIP はリダイレクト方式で direct_post.jwt を必須化(経路上に平文の属性を残さないため)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>response_mode=direct_post.jwt</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>提示レスポンスを Verifier へ直接POSTし JWE 暗号化する応答モード。</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>素の VP は複数モードから選択可。HAIP はリダイレクト方式で direct_post.jwt 必須。</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>OID4VP §Response Mode direct_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>レスポンス暗号化(JWE: ECDH-ES + A128GCM)</t>
@@ -1087,17 +1257,27 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>VP トークンを Verifier の公開鍵宛に暗号化。alg=ECDH-ES(P-256)、enc=A128GCM。</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>素の VP では暗号化は任意(enc デフォルト A128GCM)。HAIP はアルゴリズムを固定して必須化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+          <t>{ "alg": "ECDH-ES", "enc": "A128GCM", "epk": { "kty":"EC","crv":"P-256",... } }</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>VPトークンを Verifier の公開鍵宛に暗号化。</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>素の VP では暗号化は任意(enc デフォルト A128GCM)。HAIP はアルゴリズム固定で必須化。</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>OID4VP §Response Encryption</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>認可リクエストごとのエフェメラル暗号鍵</t>
         </is>
@@ -1117,18 +1297,28 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>"client_metadata": { "jwks": { "keys": [ {"kty":"EC","use":"enc","crv":"P-256",...} ] } }</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>レスポンス暗号化に、リクエスト単位の使い捨て鍵を使う。</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>鍵の使い回しによるレスポンス相関(トラッキング)防止のため HAIP で必須化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="108" customHeight="1">
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>鍵使い回しによるレスポンス相関(追跡)防止のため HAIP で必須化。</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Presentations</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="57" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>client_id プレフィックス = x509_hash</t>
@@ -1151,17 +1341,27 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
+          <t>client_id=x509_hash:Uvcpq0Yn6...gAsr8B</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
           <t>Verifier の身元識別方式。x509_hash は証明書ハッシュで識別。</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>素の VP は redirect_uri / x509_san_dns / x509_hash / did / verifier_attestation 等から選択可。HAIP は x509_hash のみを必須(draft-04 で x509_san_dns を廃止)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>素の VP は複数プレフィックスから選択可。HAIP は x509_hash のみ必須(draft-04で x509_san_dns 廃止)。</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>OID4VP §Client Identifier Prefix</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>署名付きリクエスト(JAR / RFC9101)</t>
         </is>
@@ -1176,23 +1376,33 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>request_uri=https%3A%2F%2Fverifier.example.com%2Freq%2F5Fd  →  ヘッダ { "alg":"ES256","x5c":["MIID..."] }</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>認可リクエストを署名付き JWT(request_uri 参照渡し)にする。</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>素の VP では署名可否は client_id プレフィックス依存(x509系は署名必須、redirect_uri は署名不可)。HAIP はリダイレクト方式で JAR を必須化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="76" customHeight="1">
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>素の VP では署名可否は client_id プレフィックス依存。HAIP はリダイレクト方式で JAR 必須。</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>OID4VP §Signed Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="87" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>クエリ言語 = DCQL(dcql_query)</t>
@@ -1208,24 +1418,34 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>提示要求(どのクレデンシャルのどの属性か)を記述する専用クエリ言語。</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>OID4VP 1.0 Final で DCQL に一本化され presentation_definition は廃止。HAIP も DCQL 必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+          <t>{ "credentials": [ { "id":"e","format":"dc+sd-jwt","meta":{"vct_values":[...]},"claims":[{"path":["family_name"]}] } ] }</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>提示要求を記述する専用クエリ言語。</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>OID4VP 1.0 Final で DCQL に一本化、presentation_definition 廃止。HAIP も DCQL 必須。</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>OID4VP §Digital Credentials Query Language</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="72" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>aki ベース Trusted Authorities クエリ</t>
         </is>
@@ -1245,18 +1465,28 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>どの発行者(トラストアンカー)由来かを Authority Key Identifier で絞り込む DCQL 機能。</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>"trusted_authorities": [ { "type": "aki", "values": ["s9tIpPmhxdiuNkHMEWNpYim8S8Y"] } ]</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>発行者(トラストアンカー)を Authority Key Identifier で絞り込む DCQL 機能。</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>HAIP で必須化。信頼する発行者を提示要求段階で限定するため。</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="76" customHeight="1">
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>OID4VP §Digital Credentials Query Language</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="57" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>KB-JWT(Key Binding / 持ち主証明)</t>
@@ -1272,24 +1502,34 @@
           <t>対象外</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>条件付き</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>提示時に Holder が秘密鍵で nonce/aud/sd_hash に署名し、正当な持ち主であることを示す。</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>素の SD-JWT VC では holder binding がある場合に必要。HAIP は holder binding 必須のため常時必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+          <t>~eyJ0eXAiOiJrYitqd3QiLCJhbGciOiJFUzI1NiJ9.eyJub25jZSI6Im4tMFM2Iiwi...</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>提示時に Holder が秘密鍵で nonce/aud/sd_hash に署名し持ち主を証明。</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>素の SD-JWT VC は holder binding 時に必要。HAIP は holder binding 必須のため常時必須。</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>DC API 経由の OID4VP(dc_api.jwt)</t>
         </is>
@@ -1309,14 +1549,24 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>ブラウザ/OS の Digital Credentials API 経由でやり取りする経路。</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>素の VP では DC API はリダイレクトと並列の任意選択肢。HAIP は DC API を使う場合 dc_api.jwt を必須化。</t>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>navigator.credentials.get({ digital: { requests: [ { protocol:"openid4vp", data:{...} } ] } })</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>ブラウザ/OS の Digital Credentials API 経由の経路。</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>素の VP では DC API はリダイレクトと並列の任意選択肢。HAIP は使う場合 dc_api.jwt 必須。</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>OID4VP §Digital Credentials API (DC API)</t>
         </is>
       </c>
     </row>
@@ -1331,8 +1581,10 @@
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="57" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>フォーマット SD-JWT VC(dc+sd-jwt)</t>
@@ -1355,17 +1607,27 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
+          <t>eyJ0eXAiOiJkYytzZC1qd3QiLCJhbGciOiJFUzI1NiJ9.eyJfc2QiOls...~WyJfMjZi...~</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
           <t>選択的開示に対応した JWT ベースのクレデンシャル形式。</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>HAIP は SD-JWT VC と mdoc の少なくとも一方を必須(ウォレットは両対応)。素の VCI/VP はフォーマット非依存で任意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="46" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>HAIP は SD-JWT VC と mdoc の少なくとも一方を必須。素の VCI/VP はフォーマット非依存で任意。</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="57" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>フォーマット ISO mdoc(mso_mdoc)</t>
         </is>
@@ -1385,18 +1647,28 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>"format": "mso_mdoc"  (CBOR/COSE エンコードの DeviceResponse)</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>ISO/IEC 18013-5 のモバイル文書形式(mDL 等)。</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>同上。HAIP は SD-JWT VC / mdoc の二択で少なくとも一方必須。</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §ISO Mobile Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>署名アルゴリズム ES256(P-256)</t>
@@ -1419,17 +1691,27 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
+          <t>{ "alg": "ES256" }   /   COSE alg: -7</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
           <t>クレデンシャル・各種 JWT の署名に用いる楕円曲線アルゴリズム。</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>HAIP は ES256/P-256 をベースラインとして必須化。素の仕様はアルゴリズムをプロファイルに委譲し規定しない。</t>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>HAIP は ES256/P-256 をベースライン必須。素の仕様はアルゴリズムをプロファイルに委譲。</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §Crypto Suites</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>ハッシュアルゴリズム SHA-256</t>
         </is>
@@ -1449,18 +1731,28 @@
           <t>規定なし</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>"_sd_alg": "sha-256"</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>SD-JWT のディスクロージャ等に用いるハッシュ。</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>HAIP は SHA-256 を必須。素の仕様は規定せずプロファイル委譲。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>HAIP は SHA-256 必須。素の仕様は規定せずプロファイル委譲。</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Hash Algorithms</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="72" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>失効管理(IETF Token Status List)</t>
@@ -1483,17 +1775,27 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>VC の有効性をビット列で配布し、失効を機械的に確認可能にする。</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>HAIP は exp と status の両メカニズムへの対応を必須化。素の仕様では失効方式は任意/フォーマット依存。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+          <t>"status": { "status_list": { "idx": 412, "uri": "https://issuer.example.com/statuslists/1" } }</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>VC の有効性をビット列で配布し失効を機械的に確認可能に。</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>HAIP は exp と status の両メカニズム対応を必須化。素の仕様では失効方式は任意/フォーマット依存。</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Issuer 鍵解決 = X.509(x5c にチェーン内包)</t>
         </is>
@@ -1513,27 +1815,66 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>SD-JWT VC の署名検証鍵を x5c の証明書チェーンで提供(JWKS 問い合わせ不要)。</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>HAIP は X.509 ベースを唯一の必須メカニズムに(自己署名不可・トラストアンカーは非内包)。素の仕様は鍵解決方式に中立。</t>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>{ "typ": "dc+sd-jwt", "alg": "ES256", "x5c": ["MIIDVerifierCert...", "MIIDIntermediate..."] }</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>SD-JWT VC の署名検証鍵を x5c の証明書チェーンで提供。</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>HAIP は X.509 を唯一の必須メカニズムに(自己署名不可・アンカー非内包)。素の仕様は鍵解決に中立。</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F34"/>
+  <autoFilter ref="A4:H34"/>
   <mergeCells count="6">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/07_haip-diff-matrix.xlsx
+++ b/docs/07_haip-diff-matrix.xlsx
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -724,7 +724,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>対象外</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>HAIP でも MUST ではない(authorization_code のみ必須)。利便性のため任意併用可。</t>
+          <t>HAIP はプロファイル対象外(本文に pre-authorized_code の言及なし。authorization code flow のみをプロファイル)。素の OID4VCI では任意で利用可。</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
